--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260615.xlsx
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10,623,248</t>
+          <t>13,674,274</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>13,674,274</t>
+          <t>10,623,248</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
